--- a/Lab_4/data/partB/param_optimization_process/v100_k10_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k10_s150_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
         <v>7</v>
       </c>
-      <c r="N2" t="n">
-        <v>2</v>
-      </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -573,13 +573,13 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -594,13 +594,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,16 +646,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -674,37 +674,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -716,7 +716,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -726,43 +726,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>7</v>
       </c>
       <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
-      </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -787,13 +787,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -802,25 +802,25 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
@@ -854,22 +854,22 @@
         <v>39</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -894,37 +894,37 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
         <v>4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -937,19 +937,19 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -958,19 +958,19 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>2</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,22 +998,22 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
         <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1041,16 +1041,16 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1062,25 +1062,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1090,46 +1090,46 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>5</v>
       </c>
       <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1142,28 +1142,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="F14" t="n">
-        <v>17</v>
-      </c>
-      <c r="G14" t="n">
-        <v>9</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -1175,16 +1175,16 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1197,16 +1197,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,49 +1246,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
         <v>4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" t="n">
         <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14595,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17791,7 +17791,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19372,7 +19372,7 @@
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22925,7 +22925,7 @@
       </c>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23095,7 +23095,7 @@
       </c>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="C1299" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23673,7 +23673,7 @@
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25560,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25968,7 +25968,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26716,7 +26716,7 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
